--- a/7rmartsupermarket/src/test/resources/Test Data1.xlsx
+++ b/7rmartsupermarket/src/test/resources/Test Data1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jolly\eclipse-workspace\7rmartsupermarket\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jolly\git\repository2\7rmartsupermarket\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12CF0B5-5FC6-4F46-BC53-45CC699900BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B87C48E-457A-41E1-8DC9-E006DECD4CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4248" yWindow="2064" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{200C0E7E-0C42-4940-9F34-0823F7D014D6}"/>
+    <workbookView xWindow="4248" yWindow="2064" windowWidth="17280" windowHeight="8880" activeTab="5" xr2:uid="{200C0E7E-0C42-4940-9F34-0823F7D014D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Login Page" sheetId="1" r:id="rId1"/>
@@ -65,12 +65,6 @@
     <t>type</t>
   </si>
   <si>
-    <t>anz</t>
-  </si>
-  <si>
-    <t>anc</t>
-  </si>
-  <si>
     <t>category</t>
   </si>
   <si>
@@ -93,6 +87,12 @@
   </si>
   <si>
     <t>deliverycgarge</t>
+  </si>
+  <si>
+    <t>ashlie</t>
+  </si>
+  <si>
+    <t>ash</t>
   </si>
 </sst>
 </file>
@@ -532,7 +532,7 @@
         <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -540,10 +540,10 @@
         <v>8867</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D2">
         <v>11</v>
@@ -570,12 +570,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -598,7 +598,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -616,12 +616,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -647,10 +647,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
         <v>2</v>

--- a/7rmartsupermarket/src/test/resources/Test Data1.xlsx
+++ b/7rmartsupermarket/src/test/resources/Test Data1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jolly\git\repository2\7rmartsupermarket\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B87C48E-457A-41E1-8DC9-E006DECD4CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F17C0296-7301-401A-9F14-4805ED3AAC7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4248" yWindow="2064" windowWidth="17280" windowHeight="8880" activeTab="5" xr2:uid="{200C0E7E-0C42-4940-9F34-0823F7D014D6}"/>
+    <workbookView xWindow="4248" yWindow="2064" windowWidth="17280" windowHeight="8880" firstSheet="1" activeTab="6" xr2:uid="{200C0E7E-0C42-4940-9F34-0823F7D014D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Login Page" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="foot" sheetId="5" r:id="rId4"/>
     <sheet name="news" sheetId="6" r:id="rId5"/>
     <sheet name="adminuser" sheetId="3" r:id="rId6"/>
+    <sheet name="boy" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
   <si>
     <t>username</t>
   </si>
@@ -93,6 +94,27 @@
   </si>
   <si>
     <t>ash</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>addr</t>
+  </si>
+  <si>
+    <t>kollam</t>
+  </si>
+  <si>
+    <t>umname</t>
+  </si>
+  <si>
+    <t>abi</t>
+  </si>
+  <si>
+    <t>abi@gamil.com</t>
+  </si>
+  <si>
+    <t>abiwer</t>
   </si>
 </sst>
 </file>
@@ -659,4 +681,61 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{033543E6-C567-44BC-8595-768D9323D275}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2">
+        <v>3333</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{5637502D-B17E-4727-BCD0-E438E413635E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/7rmartsupermarket/src/test/resources/Test Data1.xlsx
+++ b/7rmartsupermarket/src/test/resources/Test Data1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jolly\git\repository2\7rmartsupermarket\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F17C0296-7301-401A-9F14-4805ED3AAC7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305B2544-86FD-4B93-82A9-9E25C882A857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4248" yWindow="2064" windowWidth="17280" windowHeight="8880" firstSheet="1" activeTab="6" xr2:uid="{200C0E7E-0C42-4940-9F34-0823F7D014D6}"/>
+    <workbookView xWindow="4248" yWindow="2064" windowWidth="17280" windowHeight="8880" firstSheet="1" activeTab="4" xr2:uid="{200C0E7E-0C42-4940-9F34-0823F7D014D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Login Page" sheetId="1" r:id="rId1"/>
@@ -78,9 +78,6 @@
     <t>news</t>
   </si>
   <si>
-    <t>New product asian carrot added</t>
-  </si>
-  <si>
     <t>anc@gmail.com</t>
   </si>
   <si>
@@ -90,12 +87,6 @@
     <t>deliverycgarge</t>
   </si>
   <si>
-    <t>ashlie</t>
-  </si>
-  <si>
-    <t>ash</t>
-  </si>
-  <si>
     <t>name</t>
   </si>
   <si>
@@ -108,13 +99,22 @@
     <t>umname</t>
   </si>
   <si>
-    <t>abi</t>
-  </si>
-  <si>
-    <t>abi@gamil.com</t>
-  </si>
-  <si>
-    <t>abiwer</t>
+    <t>anu</t>
+  </si>
+  <si>
+    <t>anz</t>
+  </si>
+  <si>
+    <t>abin</t>
+  </si>
+  <si>
+    <t>abin@gamil.com</t>
+  </si>
+  <si>
+    <t>abiner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New product asian nuts added </t>
   </si>
 </sst>
 </file>
@@ -554,7 +554,7 @@
         <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -562,10 +562,10 @@
         <v>8867</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
         <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
       </c>
       <c r="D2">
         <v>11</v>
@@ -643,7 +643,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -669,10 +669,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
         <v>2</v>
@@ -694,7 +694,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B1" t="s">
         <v>6</v>
@@ -703,10 +703,10 @@
         <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F1" t="s">
         <v>1</v>
@@ -714,22 +714,22 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2">
+        <v>7333</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
         <v>26</v>
       </c>
-      <c r="C2">
-        <v>3333</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>27</v>
-      </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
